--- a/stata_strata3.xlsx
+++ b/stata_strata3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38b97e870d12de33/Documents/UAH/PhD Documents/INEdatos/Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5639FEBD-574E-4003-907A-F1E6AACBAB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{5639FEBD-574E-4003-907A-F1E6AACBAB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A55764E-74F1-4A1A-889B-6B1D255AE50E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3361699A-084A-474C-8EFC-9436150E1DD9}"/>
   </bookViews>
@@ -558,24 +558,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72CF0E9C-C438-45D9-9BB1-F83F5B8BB726}">
   <dimension ref="A1:X113"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="9.5546875" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="15" width="9.5546875" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="15.77734375" customWidth="1"/>
-    <col min="17" max="18" width="13.33203125" customWidth="1"/>
-    <col min="19" max="19" width="9.21875" customWidth="1"/>
-    <col min="20" max="20" width="11.5546875" customWidth="1"/>
-    <col min="21" max="22" width="12.21875" customWidth="1"/>
-    <col min="23" max="23" width="14.33203125" customWidth="1"/>
+    <col min="1" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="9.5703125" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+    <col min="17" max="18" width="13.28515625" customWidth="1"/>
+    <col min="19" max="19" width="9.28515625" customWidth="1"/>
+    <col min="20" max="20" width="11.5703125" customWidth="1"/>
+    <col min="21" max="22" width="12.28515625" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -646,7 +643,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>11151</v>
       </c>
@@ -718,7 +715,7 @@
       </c>
       <c r="X2" s="1"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>11111</v>
       </c>
@@ -790,7 +787,7 @@
       </c>
       <c r="X3" s="1"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>11121</v>
       </c>
@@ -862,7 +859,7 @@
       </c>
       <c r="X4" s="1"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>11152</v>
       </c>
@@ -934,7 +931,7 @@
       </c>
       <c r="X5" s="1"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>11141</v>
       </c>
@@ -1006,7 +1003,7 @@
       </c>
       <c r="X6" s="1"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>12151</v>
       </c>
@@ -1078,7 +1075,7 @@
       </c>
       <c r="X7" s="1"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>11251</v>
       </c>
@@ -1150,7 +1147,7 @@
       </c>
       <c r="X8" s="1"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11161</v>
       </c>
@@ -1222,7 +1219,7 @@
       </c>
       <c r="X9" s="1"/>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>21151</v>
       </c>
@@ -1294,7 +1291,7 @@
       </c>
       <c r="X10" s="1"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11112</v>
       </c>
@@ -1366,7 +1363,7 @@
       </c>
       <c r="X11" s="1"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11122</v>
       </c>
@@ -1438,7 +1435,7 @@
       </c>
       <c r="X12" s="1"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12111</v>
       </c>
@@ -1510,7 +1507,7 @@
       </c>
       <c r="X13" s="1"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12121</v>
       </c>
@@ -1582,7 +1579,7 @@
       </c>
       <c r="X14" s="1"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11252</v>
       </c>
@@ -1654,7 +1651,7 @@
       </c>
       <c r="X15" s="1"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>11142</v>
       </c>
@@ -1726,7 +1723,7 @@
       </c>
       <c r="X16" s="1"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>11131</v>
       </c>
@@ -1798,7 +1795,7 @@
       </c>
       <c r="X17" s="1"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>11211</v>
       </c>
@@ -1870,7 +1867,7 @@
       </c>
       <c r="X18" s="1"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>12152</v>
       </c>
@@ -1942,7 +1939,7 @@
       </c>
       <c r="X19" s="1"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>11241</v>
       </c>
@@ -2014,7 +2011,7 @@
       </c>
       <c r="X20" s="1"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>12251</v>
       </c>
@@ -2086,7 +2083,7 @@
       </c>
       <c r="X21" s="1"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>12141</v>
       </c>
@@ -2158,7 +2155,7 @@
       </c>
       <c r="X22" s="1"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>11162</v>
       </c>
@@ -2230,7 +2227,7 @@
       </c>
       <c r="X23" s="1"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21111</v>
       </c>
@@ -2302,7 +2299,7 @@
       </c>
       <c r="X24" s="1"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>11261</v>
       </c>
@@ -2374,7 +2371,7 @@
       </c>
       <c r="X25" s="1"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>12131</v>
       </c>
@@ -2446,7 +2443,7 @@
       </c>
       <c r="X26" s="1"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>12161</v>
       </c>
@@ -2518,7 +2515,7 @@
       </c>
       <c r="X27" s="1"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>11221</v>
       </c>
@@ -2590,7 +2587,7 @@
       </c>
       <c r="X28" s="1"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>12112</v>
       </c>
@@ -2662,7 +2659,7 @@
       </c>
       <c r="X29" s="1"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>11132</v>
       </c>
@@ -2734,7 +2731,7 @@
       </c>
       <c r="X30" s="1"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>21251</v>
       </c>
@@ -2806,7 +2803,7 @@
       </c>
       <c r="X31" s="1"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>21152</v>
       </c>
@@ -2878,7 +2875,7 @@
       </c>
       <c r="X32" s="1"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>21141</v>
       </c>
@@ -2950,7 +2947,7 @@
       </c>
       <c r="X33" s="1"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>11231</v>
       </c>
@@ -3022,7 +3019,7 @@
       </c>
       <c r="X34" s="1"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>21121</v>
       </c>
@@ -3094,7 +3091,7 @@
       </c>
       <c r="X35" s="1"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>11212</v>
       </c>
@@ -3166,7 +3163,7 @@
       </c>
       <c r="X36" s="1"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>21131</v>
       </c>
@@ -3238,7 +3235,7 @@
       </c>
       <c r="X37" s="1"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>11242</v>
       </c>
@@ -3310,7 +3307,7 @@
       </c>
       <c r="X38" s="1"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>22151</v>
       </c>
@@ -3382,7 +3379,7 @@
       </c>
       <c r="X39" s="1"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>11171</v>
       </c>
@@ -3454,7 +3451,7 @@
       </c>
       <c r="X40" s="1"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>12211</v>
       </c>
@@ -3526,7 +3523,7 @@
       </c>
       <c r="X41" s="1"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>12122</v>
       </c>
@@ -3598,7 +3595,7 @@
       </c>
       <c r="X42" s="1"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>12142</v>
       </c>
@@ -3670,7 +3667,7 @@
       </c>
       <c r="X43" s="1"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>21161</v>
       </c>
@@ -3742,7 +3739,7 @@
       </c>
       <c r="X44" s="1"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>11222</v>
       </c>
@@ -3814,7 +3811,7 @@
       </c>
       <c r="X45" s="1"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>21112</v>
       </c>
@@ -3886,7 +3883,7 @@
       </c>
       <c r="X46" s="1"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>12252</v>
       </c>
@@ -3958,7 +3955,7 @@
       </c>
       <c r="X47" s="1"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>12241</v>
       </c>
@@ -4030,7 +4027,7 @@
       </c>
       <c r="X48" s="1"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>12221</v>
       </c>
@@ -4102,7 +4099,7 @@
       </c>
       <c r="X49" s="1"/>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>22111</v>
       </c>
@@ -4174,7 +4171,7 @@
       </c>
       <c r="X50" s="1"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>21122</v>
       </c>
@@ -4246,7 +4243,7 @@
       </c>
       <c r="X51" s="1"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>11262</v>
       </c>
@@ -4318,7 +4315,7 @@
       </c>
       <c r="X52" s="1"/>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>12132</v>
       </c>
@@ -4390,7 +4387,7 @@
       </c>
       <c r="X53" s="1"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>21142</v>
       </c>
@@ -4462,7 +4459,7 @@
       </c>
       <c r="X54" s="1"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>11232</v>
       </c>
@@ -4534,7 +4531,7 @@
       </c>
       <c r="X55" s="1"/>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>21211</v>
       </c>
@@ -4606,7 +4603,7 @@
       </c>
       <c r="X56" s="1"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>12162</v>
       </c>
@@ -4678,7 +4675,7 @@
       </c>
       <c r="X57" s="1"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>12171</v>
       </c>
@@ -4750,7 +4747,7 @@
       </c>
       <c r="X58" s="1"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>11172</v>
       </c>
@@ -4822,7 +4819,7 @@
       </c>
       <c r="X59" s="1"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>21132</v>
       </c>
@@ -4894,7 +4891,7 @@
       </c>
       <c r="X60" s="1"/>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>12222</v>
       </c>
@@ -4966,7 +4963,7 @@
       </c>
       <c r="X61" s="1"/>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>21162</v>
       </c>
@@ -5038,7 +5035,7 @@
       </c>
       <c r="X62" s="1"/>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>12261</v>
       </c>
@@ -5110,7 +5107,7 @@
       </c>
       <c r="X63" s="1"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>22141</v>
       </c>
@@ -5182,7 +5179,7 @@
       </c>
       <c r="X64" s="1"/>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>12231</v>
       </c>
@@ -5254,7 +5251,7 @@
       </c>
       <c r="X65" s="1"/>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>21252</v>
       </c>
@@ -5326,7 +5323,7 @@
       </c>
       <c r="X66" s="1"/>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>12212</v>
       </c>
@@ -5398,7 +5395,7 @@
       </c>
       <c r="X67" s="1"/>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>22121</v>
       </c>
@@ -5470,7 +5467,7 @@
       </c>
       <c r="X68" s="1"/>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>12242</v>
       </c>
@@ -5542,7 +5539,7 @@
       </c>
       <c r="X69" s="1"/>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>21241</v>
       </c>
@@ -5614,7 +5611,7 @@
       </c>
       <c r="X70" s="1"/>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>21221</v>
       </c>
@@ -5686,7 +5683,7 @@
       </c>
       <c r="X71" s="1"/>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>22131</v>
       </c>
@@ -5758,7 +5755,7 @@
       </c>
       <c r="X72" s="1"/>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>22161</v>
       </c>
@@ -5830,7 +5827,7 @@
       </c>
       <c r="X73" s="1"/>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>22251</v>
       </c>
@@ -5902,7 +5899,7 @@
       </c>
       <c r="X74" s="1"/>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>21212</v>
       </c>
@@ -5974,7 +5971,7 @@
       </c>
       <c r="X75" s="1"/>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>22112</v>
       </c>
@@ -6046,7 +6043,7 @@
       </c>
       <c r="X76" s="1"/>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>12262</v>
       </c>
@@ -6118,7 +6115,7 @@
       </c>
       <c r="X77" s="1"/>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>12232</v>
       </c>
@@ -6190,7 +6187,7 @@
       </c>
       <c r="X78" s="1"/>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>22152</v>
       </c>
@@ -6262,7 +6259,7 @@
       </c>
       <c r="X79" s="1"/>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>21242</v>
       </c>
@@ -6334,7 +6331,7 @@
       </c>
       <c r="X80" s="1"/>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>21231</v>
       </c>
@@ -6406,7 +6403,7 @@
       </c>
       <c r="X81" s="1"/>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>21261</v>
       </c>
@@ -6478,7 +6475,7 @@
       </c>
       <c r="X82" s="1"/>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>21171</v>
       </c>
@@ -6550,7 +6547,7 @@
       </c>
       <c r="X83" s="1"/>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>22211</v>
       </c>
@@ -6622,7 +6619,7 @@
       </c>
       <c r="X84" s="1"/>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>12271</v>
       </c>
@@ -6694,7 +6691,7 @@
       </c>
       <c r="X85" s="1"/>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>21222</v>
       </c>
@@ -6766,7 +6763,7 @@
       </c>
       <c r="X86" s="1"/>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>12172</v>
       </c>
@@ -6838,7 +6835,7 @@
       </c>
       <c r="X87" s="1"/>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>11272</v>
       </c>
@@ -6910,7 +6907,7 @@
       </c>
       <c r="X88" s="1"/>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>22142</v>
       </c>
@@ -6982,7 +6979,7 @@
       </c>
       <c r="X89" s="1"/>
     </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>21172</v>
       </c>
@@ -7054,7 +7051,7 @@
       </c>
       <c r="X90" s="1"/>
     </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>11271</v>
       </c>
@@ -7126,7 +7123,7 @@
       </c>
       <c r="X91" s="1"/>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>22122</v>
       </c>
@@ -7198,7 +7195,7 @@
       </c>
       <c r="X92" s="1"/>
     </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>21262</v>
       </c>
@@ -7270,7 +7267,7 @@
       </c>
       <c r="X93" s="1"/>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>12272</v>
       </c>
@@ -7342,7 +7339,7 @@
       </c>
       <c r="X94" s="1"/>
     </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>22241</v>
       </c>
@@ -7414,7 +7411,7 @@
       </c>
       <c r="X95" s="1"/>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>22231</v>
       </c>
@@ -7486,7 +7483,7 @@
       </c>
       <c r="X96" s="1"/>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>22252</v>
       </c>
@@ -7558,7 +7555,7 @@
       </c>
       <c r="X97" s="1"/>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>22221</v>
       </c>
@@ -7630,7 +7627,7 @@
       </c>
       <c r="X98" s="1"/>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>21232</v>
       </c>
@@ -7702,7 +7699,7 @@
       </c>
       <c r="X99" s="1"/>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>22162</v>
       </c>
@@ -7774,7 +7771,7 @@
       </c>
       <c r="X100" s="1"/>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>22132</v>
       </c>
@@ -7846,7 +7843,7 @@
       </c>
       <c r="X101" s="1"/>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>22261</v>
       </c>
@@ -7918,7 +7915,7 @@
       </c>
       <c r="X102" s="1"/>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>22212</v>
       </c>
@@ -7990,7 +7987,7 @@
       </c>
       <c r="X103" s="1"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>22171</v>
       </c>
@@ -8062,7 +8059,7 @@
       </c>
       <c r="X104" s="1"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>22222</v>
       </c>
@@ -8134,7 +8131,7 @@
       </c>
       <c r="X105" s="1"/>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>21272</v>
       </c>
@@ -8206,7 +8203,7 @@
       </c>
       <c r="X106" s="1"/>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>22242</v>
       </c>
@@ -8278,7 +8275,7 @@
       </c>
       <c r="X107" s="1"/>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>21271</v>
       </c>
@@ -8350,7 +8347,7 @@
       </c>
       <c r="X108" s="1"/>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>22232</v>
       </c>
@@ -8422,7 +8419,7 @@
       </c>
       <c r="X109" s="1"/>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>22262</v>
       </c>
@@ -8494,7 +8491,7 @@
       </c>
       <c r="X110" s="1"/>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>22172</v>
       </c>
@@ -8566,7 +8563,7 @@
       </c>
       <c r="X111" s="1"/>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>22271</v>
       </c>
@@ -8638,7 +8635,7 @@
       </c>
       <c r="X112" s="1"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>22272</v>
       </c>
